--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3143,6 +3143,103 @@
       <c r="AY24" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131736097</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91848</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stormyran Nordost, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>638181</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7033858</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Susanne Ek</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>131736097</v>
       </c>
       <c r="B25" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>131736097</v>
       </c>
       <c r="B25" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>131736097</v>
       </c>
       <c r="B25" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>131736097</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>131736097</v>
       </c>
       <c r="B25" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>131736097</v>
       </c>
       <c r="B25" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>131736097</v>
       </c>
       <c r="B25" t="n">
-        <v>91868</v>
+        <v>91904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>131736097</v>
       </c>
       <c r="B25" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3242,6 +3242,1384 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133757873</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bergvattbäcken, Bergvattbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>638274</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7033693</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133757536</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>638251</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7033758</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133758839</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hundberget, Hundberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>638041</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7033826</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133757936</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bergvattbäcken, Bergvattbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>638259</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7033685</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133757965</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bergvattbäcken, Bergvattbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>638255</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7033681</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133758708</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hundberget, Hundberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>638056</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7033801</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133758813</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hundberget, Hundberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>638048</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7033825</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133757409</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>638268</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7033770</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133757332</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>638264</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7033779</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133757629</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>638286</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7033725</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133757380</v>
+      </c>
+      <c r="B36" t="n">
+        <v>89300</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>510</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>638266</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7033766</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133758276</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hundberget, Hundberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>638162</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7033688</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133758302</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hundberget, Hundberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>638162</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7033688</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133758032</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bergvattbäcken, Bergvattbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>638230</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7033673</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3355,7 +3355,7 @@
         <v>133757536</v>
       </c>
       <c r="B27" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>133758839</v>
       </c>
       <c r="B28" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>133757936</v>
       </c>
       <c r="B29" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>133757965</v>
       </c>
       <c r="B30" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>133758708</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>133757409</v>
       </c>
       <c r="B33" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>133757332</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>133757629</v>
       </c>
       <c r="B35" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>133757380</v>
       </c>
       <c r="B36" t="n">
-        <v>89300</v>
+        <v>89302</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4332,32 +4332,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133758276</v>
+        <v>133758302</v>
       </c>
       <c r="B37" t="n">
-        <v>80438</v>
+        <v>80475</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4429,32 +4429,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133758302</v>
+        <v>133758276</v>
       </c>
       <c r="B38" t="n">
-        <v>80474</v>
+        <v>80439</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,7 +4529,7 @@
         <v>133758032</v>
       </c>
       <c r="B39" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3452,7 +3452,7 @@
         <v>133758839</v>
       </c>
       <c r="B28" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,32 +3546,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133757936</v>
+        <v>133757965</v>
       </c>
       <c r="B29" t="n">
-        <v>91920</v>
+        <v>91889</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638259</v>
+        <v>638255</v>
       </c>
       <c r="R29" t="n">
-        <v>7033685</v>
+        <v>7033681</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133757965</v>
+        <v>133757936</v>
       </c>
       <c r="B30" t="n">
-        <v>91883</v>
+        <v>91926</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638255</v>
+        <v>638259</v>
       </c>
       <c r="R30" t="n">
-        <v>7033681</v>
+        <v>7033685</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133757409</v>
+        <v>133757332</v>
       </c>
       <c r="B33" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638268</v>
+        <v>638264</v>
       </c>
       <c r="R33" t="n">
-        <v>7033770</v>
+        <v>7033779</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133757332</v>
+        <v>133757409</v>
       </c>
       <c r="B34" t="n">
-        <v>79334</v>
+        <v>91926</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638264</v>
+        <v>638268</v>
       </c>
       <c r="R34" t="n">
-        <v>7033779</v>
+        <v>7033770</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4141,7 +4141,7 @@
         <v>133757629</v>
       </c>
       <c r="B35" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>133757380</v>
       </c>
       <c r="B36" t="n">
-        <v>89302</v>
+        <v>89308</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3452,7 +3452,7 @@
         <v>133758839</v>
       </c>
       <c r="B28" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,32 +3546,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133757965</v>
+        <v>133757936</v>
       </c>
       <c r="B29" t="n">
-        <v>91889</v>
+        <v>91928</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638255</v>
+        <v>638259</v>
       </c>
       <c r="R29" t="n">
-        <v>7033681</v>
+        <v>7033685</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133757936</v>
+        <v>133757965</v>
       </c>
       <c r="B30" t="n">
-        <v>91926</v>
+        <v>91891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638259</v>
+        <v>638255</v>
       </c>
       <c r="R30" t="n">
-        <v>7033685</v>
+        <v>7033681</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133757332</v>
+        <v>133757409</v>
       </c>
       <c r="B33" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638264</v>
+        <v>638268</v>
       </c>
       <c r="R33" t="n">
-        <v>7033779</v>
+        <v>7033770</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133757409</v>
+        <v>133757332</v>
       </c>
       <c r="B34" t="n">
-        <v>91926</v>
+        <v>79334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638268</v>
+        <v>638264</v>
       </c>
       <c r="R34" t="n">
-        <v>7033770</v>
+        <v>7033779</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4138,10 +4138,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133757629</v>
+        <v>133757380</v>
       </c>
       <c r="B35" t="n">
-        <v>91926</v>
+        <v>89310</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4149,21 +4149,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638286</v>
+        <v>638266</v>
       </c>
       <c r="R35" t="n">
-        <v>7033725</v>
+        <v>7033766</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4235,10 +4235,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133757380</v>
+        <v>133757629</v>
       </c>
       <c r="B36" t="n">
-        <v>89308</v>
+        <v>91928</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,21 +4246,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638266</v>
+        <v>638286</v>
       </c>
       <c r="R36" t="n">
-        <v>7033766</v>
+        <v>7033725</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3248,7 +3248,7 @@
         <v>133757873</v>
       </c>
       <c r="B26" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>133757536</v>
       </c>
       <c r="B27" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>133758839</v>
       </c>
       <c r="B28" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,32 +3546,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133757936</v>
+        <v>133757965</v>
       </c>
       <c r="B29" t="n">
-        <v>91928</v>
+        <v>91910</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638259</v>
+        <v>638255</v>
       </c>
       <c r="R29" t="n">
-        <v>7033685</v>
+        <v>7033681</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133757965</v>
+        <v>133757936</v>
       </c>
       <c r="B30" t="n">
-        <v>91891</v>
+        <v>91947</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638255</v>
+        <v>638259</v>
       </c>
       <c r="R30" t="n">
-        <v>7033681</v>
+        <v>7033685</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3743,7 +3743,7 @@
         <v>133758708</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>133758813</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133757409</v>
+        <v>133757332</v>
       </c>
       <c r="B33" t="n">
-        <v>91928</v>
+        <v>79348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638268</v>
+        <v>638264</v>
       </c>
       <c r="R33" t="n">
-        <v>7033770</v>
+        <v>7033779</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133757332</v>
+        <v>133757409</v>
       </c>
       <c r="B34" t="n">
-        <v>79334</v>
+        <v>91947</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638264</v>
+        <v>638268</v>
       </c>
       <c r="R34" t="n">
-        <v>7033779</v>
+        <v>7033770</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4138,10 +4138,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133757380</v>
+        <v>133757629</v>
       </c>
       <c r="B35" t="n">
-        <v>89310</v>
+        <v>91947</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4149,21 +4149,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638266</v>
+        <v>638286</v>
       </c>
       <c r="R35" t="n">
-        <v>7033766</v>
+        <v>7033725</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4235,10 +4235,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133757629</v>
+        <v>133757380</v>
       </c>
       <c r="B36" t="n">
-        <v>91928</v>
+        <v>89328</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,21 +4246,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638286</v>
+        <v>638266</v>
       </c>
       <c r="R36" t="n">
-        <v>7033725</v>
+        <v>7033766</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4335,7 +4335,7 @@
         <v>133758302</v>
       </c>
       <c r="B37" t="n">
-        <v>80475</v>
+        <v>80489</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>133758276</v>
       </c>
       <c r="B38" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>133758032</v>
       </c>
       <c r="B39" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3546,32 +3546,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133757965</v>
+        <v>133757936</v>
       </c>
       <c r="B29" t="n">
-        <v>91910</v>
+        <v>91947</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638255</v>
+        <v>638259</v>
       </c>
       <c r="R29" t="n">
-        <v>7033681</v>
+        <v>7033685</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133757936</v>
+        <v>133757965</v>
       </c>
       <c r="B30" t="n">
-        <v>91947</v>
+        <v>91910</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638259</v>
+        <v>638255</v>
       </c>
       <c r="R30" t="n">
-        <v>7033685</v>
+        <v>7033681</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133757332</v>
+        <v>133757409</v>
       </c>
       <c r="B33" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638264</v>
+        <v>638268</v>
       </c>
       <c r="R33" t="n">
-        <v>7033779</v>
+        <v>7033770</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133757409</v>
+        <v>133757332</v>
       </c>
       <c r="B34" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638268</v>
+        <v>638264</v>
       </c>
       <c r="R34" t="n">
-        <v>7033770</v>
+        <v>7033779</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3248,7 +3248,7 @@
         <v>133757873</v>
       </c>
       <c r="B26" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>133757536</v>
       </c>
       <c r="B27" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>133758839</v>
       </c>
       <c r="B28" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>133757936</v>
       </c>
       <c r="B29" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>133757965</v>
       </c>
       <c r="B30" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>133758708</v>
       </c>
       <c r="B31" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>133758813</v>
       </c>
       <c r="B32" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133757409</v>
+        <v>133757332</v>
       </c>
       <c r="B33" t="n">
-        <v>91947</v>
+        <v>79358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638268</v>
+        <v>638264</v>
       </c>
       <c r="R33" t="n">
-        <v>7033770</v>
+        <v>7033779</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133757332</v>
+        <v>133757409</v>
       </c>
       <c r="B34" t="n">
-        <v>79348</v>
+        <v>91957</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638264</v>
+        <v>638268</v>
       </c>
       <c r="R34" t="n">
-        <v>7033779</v>
+        <v>7033770</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4141,7 +4141,7 @@
         <v>133757629</v>
       </c>
       <c r="B35" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>133757380</v>
       </c>
       <c r="B36" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>133758302</v>
       </c>
       <c r="B37" t="n">
-        <v>80489</v>
+        <v>80485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>133758276</v>
       </c>
       <c r="B38" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>133758032</v>
       </c>
       <c r="B39" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3944,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133757332</v>
+        <v>133757409</v>
       </c>
       <c r="B33" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638264</v>
+        <v>638268</v>
       </c>
       <c r="R33" t="n">
-        <v>7033779</v>
+        <v>7033770</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133757409</v>
+        <v>133757332</v>
       </c>
       <c r="B34" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638268</v>
+        <v>638264</v>
       </c>
       <c r="R34" t="n">
-        <v>7033770</v>
+        <v>7033779</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4138,10 +4138,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133757629</v>
+        <v>133757380</v>
       </c>
       <c r="B35" t="n">
-        <v>91957</v>
+        <v>89338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4149,21 +4149,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638286</v>
+        <v>638266</v>
       </c>
       <c r="R35" t="n">
-        <v>7033725</v>
+        <v>7033766</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4235,10 +4235,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133757380</v>
+        <v>133757629</v>
       </c>
       <c r="B36" t="n">
-        <v>89338</v>
+        <v>91957</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,21 +4246,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638266</v>
+        <v>638286</v>
       </c>
       <c r="R36" t="n">
-        <v>7033766</v>
+        <v>7033725</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3944,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133757409</v>
+        <v>133757332</v>
       </c>
       <c r="B33" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638268</v>
+        <v>638264</v>
       </c>
       <c r="R33" t="n">
-        <v>7033770</v>
+        <v>7033779</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133757332</v>
+        <v>133757409</v>
       </c>
       <c r="B34" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638264</v>
+        <v>638268</v>
       </c>
       <c r="R34" t="n">
-        <v>7033779</v>
+        <v>7033770</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4138,10 +4138,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133757380</v>
+        <v>133757629</v>
       </c>
       <c r="B35" t="n">
-        <v>89338</v>
+        <v>91957</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4149,21 +4149,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638266</v>
+        <v>638286</v>
       </c>
       <c r="R35" t="n">
-        <v>7033766</v>
+        <v>7033725</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4235,10 +4235,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133757629</v>
+        <v>133757380</v>
       </c>
       <c r="B36" t="n">
-        <v>91957</v>
+        <v>89338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,21 +4246,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638286</v>
+        <v>638266</v>
       </c>
       <c r="R36" t="n">
-        <v>7033725</v>
+        <v>7033766</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -3355,7 +3355,7 @@
         <v>133757536</v>
       </c>
       <c r="B27" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>133758839</v>
       </c>
       <c r="B28" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>133757936</v>
       </c>
       <c r="B29" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>133757965</v>
       </c>
       <c r="B30" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>133758708</v>
       </c>
       <c r="B31" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>133757332</v>
       </c>
       <c r="B33" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>133757409</v>
       </c>
       <c r="B34" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>133757629</v>
       </c>
       <c r="B35" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>133757380</v>
       </c>
       <c r="B36" t="n">
-        <v>89338</v>
+        <v>89339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>133758302</v>
       </c>
       <c r="B37" t="n">
-        <v>80485</v>
+        <v>80486</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>133758276</v>
       </c>
       <c r="B38" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>133758032</v>
       </c>
       <c r="B39" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 27491-2025 artfynd.xlsx
+++ b/artfynd/A 27491-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757380</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712753</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712795</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712796</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712797</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712799</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712802</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757409</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757629</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,6 +1716,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757936</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133758839</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712754</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1965,6 +2030,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712801</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2062,6 +2132,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757965</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712794</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2269,6 +2349,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712683</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2375,6 +2460,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712749</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2481,6 +2571,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712756</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2582,6 +2677,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712793</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2683,6 +2783,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712798</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2780,6 +2885,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757332</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2877,6 +2987,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757536</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2974,6 +3089,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133758032</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3071,6 +3191,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133758708</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3173,6 +3298,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661890</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3275,6 +3405,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661891</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3372,6 +3507,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661898</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3473,6 +3613,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712684</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3574,6 +3719,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712784</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3671,6 +3821,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133758276</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3768,6 +3923,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133758302</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3874,6 +4034,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712800</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3981,6 +4146,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757873</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4088,6 +4258,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133758813</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4190,6 +4365,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661882</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4296,6 +4476,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712751</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4402,6 +4587,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712752</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4508,6 +4698,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712757</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4614,6 +4809,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712682</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4715,6 +4915,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712755</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4822,6 +5027,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712685</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4928,8 +5138,57 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712791</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>